--- a/media/Levels/kakeraMapLevel3.xlsx
+++ b/media/Levels/kakeraMapLevel3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CEF807-062A-46E4-9C83-6AF781BD9B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961DB332-1F8C-4D87-AB03-1E83AC16E842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="15660" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Level_3" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19318,28 +19314,28 @@
         <v>0</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB63">
         <v>0</v>
@@ -19620,28 +19616,28 @@
         <v>0</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB64">
         <v>0</v>
@@ -19922,28 +19918,28 @@
         <v>0</v>
       </c>
       <c r="AT65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65">
         <v>0</v>
@@ -20224,28 +20220,28 @@
         <v>0</v>
       </c>
       <c r="AT66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB66">
         <v>0</v>
@@ -20526,28 +20522,28 @@
         <v>0</v>
       </c>
       <c r="AT67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB67">
         <v>0</v>
@@ -20828,28 +20824,28 @@
         <v>0</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB68">
         <v>0</v>
@@ -21130,28 +21126,28 @@
         <v>0</v>
       </c>
       <c r="AT69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB69">
         <v>0</v>
@@ -21432,28 +21428,28 @@
         <v>0</v>
       </c>
       <c r="AT70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB70">
         <v>0</v>
@@ -21734,28 +21730,28 @@
         <v>0</v>
       </c>
       <c r="AT71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB71">
         <v>0</v>
